--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Retirement Fund - Pure Debt Plan.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Retirement Fund - Pure Debt Plan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="75">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Retirement Fund - Pure Debt Plan</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -73,7 +73,10 @@
     <t>IN0020210137</t>
   </si>
   <si>
-    <t>IN0020230085</t>
+    <t>IN0020240035</t>
+  </si>
+  <si>
+    <t>IN0020240126</t>
   </si>
   <si>
     <t>Non-Convertible debentures / Bonds</t>
@@ -88,22 +91,22 @@
     <t>CRISIL AA</t>
   </si>
   <si>
-    <t>Power Finance Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE134E08HD5</t>
+    <t>LIC Housing Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE115A07NP6</t>
   </si>
   <si>
     <t>CRISIL AAA</t>
   </si>
   <si>
-    <t>LIC Housing Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE115A07NP6</t>
-  </si>
-  <si>
-    <t>Muthoot Finance Ltd.</t>
+    <t>Indian Railway Finance Corporation Ltd. **</t>
+  </si>
+  <si>
+    <t>INE053F07AB5</t>
+  </si>
+  <si>
+    <t>Muthoot Finance Ltd. **</t>
   </si>
   <si>
     <t>INE414G07IR6</t>
@@ -112,18 +115,6 @@
     <t>CRISIL AA+</t>
   </si>
   <si>
-    <t>Godrej Industries Ltd. **</t>
-  </si>
-  <si>
-    <t>INE233A08097</t>
-  </si>
-  <si>
-    <t>NABARD **</t>
-  </si>
-  <si>
-    <t>INE261F08DQ4</t>
-  </si>
-  <si>
     <t>Summit Digitel Infrastructure Ltd **</t>
   </si>
   <si>
@@ -139,16 +130,34 @@
     <t>ICRA A</t>
   </si>
   <si>
-    <t>Shriram Finance Ltd.</t>
+    <t>Cholamandalam Investment And Finance Company Ltd. **</t>
+  </si>
+  <si>
+    <t>INE121A08PT9</t>
+  </si>
+  <si>
+    <t>ICRA AA+</t>
+  </si>
+  <si>
+    <t>Shriram Finance Ltd. **</t>
   </si>
   <si>
     <t>INE721A07RH9</t>
   </si>
   <si>
+    <t>Eris Lifesciences Ltd. **</t>
+  </si>
+  <si>
+    <t>INE406M08011</t>
+  </si>
+  <si>
+    <t>FITCH AA</t>
+  </si>
+  <si>
     <t>Zero Coupon Bonds / Deep Discount Bonds</t>
   </si>
   <si>
-    <t>Aditya Birla Finance Ltd. **</t>
+    <t>Aditya Birla Capital Ltd. **</t>
   </si>
   <si>
     <t>INE860H07HW0</t>
@@ -214,7 +223,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -607,13 +616,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -631,8 +640,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="13763625"/>
-          <a:ext cx="3571875" cy="1905000"/>
+          <a:off x="666750" y="13906500"/>
+          <a:ext cx="4019550" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -646,13 +655,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>83</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -670,8 +679,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="16621125"/>
-          <a:ext cx="3571875" cy="1905000"/>
+          <a:off x="666750" y="16764000"/>
+          <a:ext cx="4019550" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1004,11 +1013,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J81"/>
+  <dimension ref="B1:J82"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="22" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="22" width="53.57142857142857" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="22" width="60.285714285714285" collapsed="true"/>
     <col min="3" max="3" bestFit="true" customWidth="true" style="22" width="17.142857142857142" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="22" width="9.714285714285714" collapsed="true"/>
     <col min="5" max="5" bestFit="true" customWidth="true" style="22" width="19.714285714285715" collapsed="true"/>
@@ -1104,10 +1113,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>10156.340000000002</v>
+        <v>10277.419999999998</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9470003155711001</v>
+        <v>0.9676621751922999</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1141,10 +1150,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>10156.340000000002</v>
+        <v>10277.419999999998</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9470003155711001</v>
+        <v>0.9676621751922999</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1178,10 +1187,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="9">
-        <v>5090.15</v>
+        <v>5943.59</v>
       </c>
       <c r="H9" s="10">
-        <v>0.4746172003208</v>
+        <v>0.5596139135944</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>13</v>
@@ -1204,16 +1213,16 @@
         <v>17</v>
       </c>
       <c r="F10" s="15">
-        <v>2300000</v>
+        <v>2250000</v>
       </c>
       <c r="G10" s="16">
-        <v>2355.35</v>
+        <v>2371.91</v>
       </c>
       <c r="H10" s="17">
-        <v>0.2196182082602</v>
+        <v>0.2233252693732</v>
       </c>
       <c r="I10" s="16">
-        <v>6.86</v>
+        <v>6.39</v>
       </c>
       <c r="J10" s="11" t="s">
         <v>13</v>
@@ -1227,7 +1236,7 @@
         <v>18</v>
       </c>
       <c r="D11" s="14">
-        <v>7.53</v>
+        <v>6.99</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>17</v>
@@ -1236,13 +1245,13 @@
         <v>1695100</v>
       </c>
       <c r="G11" s="16">
-        <v>1707.45</v>
+        <v>1730.30</v>
       </c>
       <c r="H11" s="17">
-        <v>0.1592065339308</v>
+        <v>0.162914998291</v>
       </c>
       <c r="I11" s="16">
-        <v>7.47</v>
+        <v>6.80</v>
       </c>
       <c r="J11" s="11" t="s">
         <v>13</v>
@@ -1256,7 +1265,7 @@
         <v>19</v>
       </c>
       <c r="D12" s="14">
-        <v>7.18</v>
+        <v>7.34</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>17</v>
@@ -1265,13 +1274,13 @@
         <v>1000000</v>
       </c>
       <c r="G12" s="16">
-        <v>1027.35</v>
+        <v>1064.43</v>
       </c>
       <c r="H12" s="17">
-        <v>0.0957924581298</v>
+        <v>0.1002205465127</v>
       </c>
       <c r="I12" s="16">
-        <v>6.87</v>
+        <v>6.98</v>
       </c>
       <c r="J12" s="11" t="s">
         <v>13</v>
@@ -1279,35 +1288,35 @@
     </row>
     <row r="13" spans="2:10" ht="15" customHeight="1">
       <c r="B13" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="14">
+        <v>6.79</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="15">
+        <v>750000</v>
+      </c>
+      <c r="G13" s="16">
+        <v>776.95</v>
+      </c>
+      <c r="H13" s="17">
+        <v>0.0731530994175</v>
+      </c>
+      <c r="I13" s="16">
+        <v>6.37</v>
       </c>
       <c r="J13" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1">
-      <c r="B14" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="9">
-        <v>4703.150000000001</v>
-      </c>
-      <c r="H14" s="10">
-        <v>0.438532437293</v>
-      </c>
-      <c r="I14" s="9" t="s">
+      <c r="B14" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J14" s="11" t="s">
@@ -1315,29 +1324,29 @@
       </c>
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1">
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="14">
-        <v>8.50</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" s="15">
-        <v>700</v>
-      </c>
-      <c r="G15" s="16">
-        <v>705.77</v>
-      </c>
-      <c r="H15" s="17">
-        <v>0.0658076051728</v>
-      </c>
-      <c r="I15" s="16">
-        <v>8.04</v>
+      <c r="C15" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="9">
+        <v>3960.8700000000003</v>
+      </c>
+      <c r="H15" s="10">
+        <v>0.3729325141769</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J15" s="11" t="s">
         <v>13</v>
@@ -1345,28 +1354,28 @@
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1">
       <c r="B16" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="14">
+        <v>8.50</v>
+      </c>
+      <c r="E16" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="14">
-        <v>8.39</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>26</v>
-      </c>
       <c r="F16" s="15">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="G16" s="16">
-        <v>700.91</v>
+        <v>711.66</v>
       </c>
       <c r="H16" s="17">
-        <v>0.0653544476836</v>
+        <v>0.0670057722266</v>
       </c>
       <c r="I16" s="16">
-        <v>7.69</v>
+        <v>7.40</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>13</v>
@@ -1374,28 +1383,28 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1">
       <c r="B17" s="12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D17" s="14">
         <v>8.75</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F17" s="15">
         <v>50</v>
       </c>
       <c r="G17" s="16">
-        <v>517.57</v>
+        <v>527.47</v>
       </c>
       <c r="H17" s="17">
-        <v>0.0482594077522</v>
+        <v>0.0496635116156</v>
       </c>
       <c r="I17" s="16">
-        <v>7.65</v>
+        <v>6.92</v>
       </c>
       <c r="J17" s="11" t="s">
         <v>13</v>
@@ -1403,28 +1412,28 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>30</v>
-      </c>
       <c r="D18" s="14">
-        <v>8.78</v>
+        <v>7.27</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F18" s="15">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="G18" s="16">
-        <v>500.82</v>
+        <v>507.19</v>
       </c>
       <c r="H18" s="17">
-        <v>0.0466975995333</v>
+        <v>0.0477540646033</v>
       </c>
       <c r="I18" s="16">
-        <v>8.66</v>
+        <v>6.50</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>13</v>
@@ -1432,28 +1441,28 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
       <c r="B19" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="14">
+        <v>8.78</v>
+      </c>
+      <c r="E19" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="14">
-        <v>7.17</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>31</v>
-      </c>
       <c r="F19" s="15">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="G19" s="16">
-        <v>498.29</v>
+        <v>506.49</v>
       </c>
       <c r="H19" s="17">
-        <v>0.0464616965605</v>
+        <v>0.047688156669</v>
       </c>
       <c r="I19" s="16">
-        <v>8.03</v>
+        <v>8.04</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>13</v>
@@ -1461,28 +1470,28 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
       <c r="B20" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>35</v>
-      </c>
       <c r="D20" s="14">
-        <v>7.25</v>
+        <v>6.59</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F20" s="15">
         <v>50</v>
       </c>
       <c r="G20" s="16">
-        <v>497.98</v>
+        <v>499.57</v>
       </c>
       <c r="H20" s="17">
-        <v>0.0464327914532</v>
+        <v>0.0470366096609</v>
       </c>
       <c r="I20" s="16">
-        <v>7.80</v>
+        <v>6.85</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>13</v>
@@ -1490,28 +1499,28 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="D21" s="14">
+        <v>8</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>37</v>
-      </c>
-      <c r="D21" s="14">
-        <v>6.59</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>26</v>
       </c>
       <c r="F21" s="15">
         <v>50</v>
       </c>
       <c r="G21" s="16">
-        <v>493.09</v>
+        <v>497.37</v>
       </c>
       <c r="H21" s="17">
-        <v>0.0459768366956</v>
+        <v>0.0468294704386</v>
       </c>
       <c r="I21" s="16">
-        <v>7.89</v>
+        <v>8.38</v>
       </c>
       <c r="J21" s="11" t="s">
         <v>13</v>
@@ -1525,22 +1534,22 @@
         <v>39</v>
       </c>
       <c r="D22" s="14">
-        <v>8</v>
+        <v>9.05</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>40</v>
       </c>
       <c r="F22" s="15">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="G22" s="16">
-        <v>489.43</v>
+        <v>307.08</v>
       </c>
       <c r="H22" s="17">
-        <v>0.0456355699445</v>
+        <v>0.0289128692569</v>
       </c>
       <c r="I22" s="16">
-        <v>9.38</v>
+        <v>8.56</v>
       </c>
       <c r="J22" s="11" t="s">
         <v>13</v>
@@ -1557,19 +1566,19 @@
         <v>8.75</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F23" s="15">
         <v>300</v>
       </c>
       <c r="G23" s="16">
-        <v>299.29</v>
+        <v>302.4</v>
       </c>
       <c r="H23" s="17">
-        <v>0.0279064824973</v>
+        <v>0.0284722276386</v>
       </c>
       <c r="I23" s="16">
-        <v>8.96</v>
+        <v>7.92</v>
       </c>
       <c r="J23" s="11" t="s">
         <v>13</v>
@@ -1577,35 +1586,35 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1">
       <c r="B24" s="12" t="s">
-        <v>13</v>
+        <v>43</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="14">
+        <v>8.73</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F24" s="15">
+        <v>100</v>
+      </c>
+      <c r="G24" s="16">
+        <v>101.64</v>
+      </c>
+      <c r="H24" s="17">
+        <v>0.0095698320674</v>
+      </c>
+      <c r="I24" s="16">
+        <v>7.60</v>
       </c>
       <c r="J24" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
-      <c r="B25" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" s="9">
-        <v>363.04</v>
-      </c>
-      <c r="H25" s="10">
-        <v>0.0338506779573</v>
-      </c>
-      <c r="I25" s="9" t="s">
+      <c r="B25" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J25" s="11" t="s">
@@ -1613,29 +1622,29 @@
       </c>
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
-      <c r="B26" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="13" t="s">
+      <c r="B26" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F26" s="15">
-        <v>30</v>
-      </c>
-      <c r="G26" s="16">
-        <v>363.04</v>
-      </c>
-      <c r="H26" s="17">
-        <v>0.0338506779573</v>
-      </c>
-      <c r="I26" s="16">
-        <v>8.03</v>
+      <c r="C26" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="9">
+        <v>372.96</v>
+      </c>
+      <c r="H26" s="10">
+        <v>0.035115747421</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J26" s="11" t="s">
         <v>13</v>
@@ -1643,35 +1652,35 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
       <c r="B27" s="12" t="s">
-        <v>13</v>
+        <v>47</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27" s="15">
+        <v>30</v>
+      </c>
+      <c r="G27" s="16">
+        <v>372.96</v>
+      </c>
+      <c r="H27" s="17">
+        <v>0.035115747421</v>
+      </c>
+      <c r="I27" s="16">
+        <v>7</v>
       </c>
       <c r="J27" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
-      <c r="B28" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H28" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I28" s="9" t="s">
+      <c r="B28" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J28" s="11" t="s">
@@ -1679,7 +1688,28 @@
       </c>
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I29" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J29" s="11" t="s">
@@ -1687,28 +1717,7 @@
       </c>
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
-      <c r="B30" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H30" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I30" s="9" t="s">
+      <c r="B30" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J30" s="11" t="s">
@@ -1716,7 +1725,28 @@
       </c>
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I31" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J31" s="11" t="s">
@@ -1724,28 +1754,7 @@
       </c>
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
-      <c r="B32" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H32" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I32" s="9" t="s">
+      <c r="B32" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J32" s="11" t="s">
@@ -1753,7 +1762,28 @@
       </c>
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I33" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J33" s="11" t="s">
@@ -1761,36 +1791,36 @@
       </c>
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" ht="15" customHeight="1">
+      <c r="B35" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J34" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10" ht="15" customHeight="1">
-      <c r="B35" s="12" t="s">
+      <c r="H35" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J35" s="11" t="s">
@@ -1798,28 +1828,7 @@
       </c>
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
-      <c r="B36" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I36" s="9" t="s">
+      <c r="B36" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J36" s="11" t="s">
@@ -1827,7 +1836,28 @@
       </c>
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I37" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J37" s="11" t="s">
@@ -1835,28 +1865,7 @@
       </c>
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
-      <c r="B38" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H38" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I38" s="9" t="s">
+      <c r="B38" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J38" s="11" t="s">
@@ -1864,7 +1873,28 @@
       </c>
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I39" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J39" s="11" t="s">
@@ -1872,28 +1902,7 @@
       </c>
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
-      <c r="B40" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H40" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I40" s="9" t="s">
+      <c r="B40" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J40" s="11" t="s">
@@ -1901,7 +1910,28 @@
       </c>
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
-      <c r="B41" s="12" t="s">
+      <c r="B41" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I41" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J41" s="11" t="s">
@@ -1909,28 +1939,7 @@
       </c>
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
-      <c r="B42" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G42" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H42" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I42" s="9" t="s">
+      <c r="B42" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J42" s="11" t="s">
@@ -1938,7 +1947,28 @@
       </c>
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
-      <c r="B43" s="12" t="s">
+      <c r="B43" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I43" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J43" s="11" t="s">
@@ -1946,28 +1976,7 @@
       </c>
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
-      <c r="B44" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H44" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I44" s="9" t="s">
+      <c r="B44" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J44" s="11" t="s">
@@ -1975,7 +1984,28 @@
       </c>
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I45" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J45" s="11" t="s">
@@ -1983,28 +2013,7 @@
       </c>
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
-      <c r="B46" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H46" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I46" s="9" t="s">
+      <c r="B46" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J46" s="11" t="s">
@@ -2012,7 +2021,28 @@
       </c>
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
-      <c r="B47" s="12" t="s">
+      <c r="B47" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I47" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J47" s="11" t="s">
@@ -2020,28 +2050,7 @@
       </c>
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
-      <c r="B48" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G48" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H48" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I48" s="9" t="s">
+      <c r="B48" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J48" s="11" t="s">
@@ -2049,7 +2058,28 @@
       </c>
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
-      <c r="B49" s="12" t="s">
+      <c r="B49" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I49" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J49" s="11" t="s">
@@ -2057,28 +2087,7 @@
       </c>
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
-      <c r="B50" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" s="9">
-        <v>236</v>
-      </c>
-      <c r="H50" s="10">
-        <v>0.022005178487</v>
-      </c>
-      <c r="I50" s="9" t="s">
+      <c r="B50" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J50" s="11" t="s">
@@ -2086,7 +2095,28 @@
       </c>
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
-      <c r="B51" s="12" t="s">
+      <c r="B51" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="9">
+        <v>210.92</v>
+      </c>
+      <c r="H51" s="10">
+        <v>0.0198590021612</v>
+      </c>
+      <c r="I51" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J51" s="11" t="s">
@@ -2094,37 +2124,16 @@
       </c>
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
-      <c r="B52" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="C52" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D52" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F52" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G52" s="19">
-        <v>332.4082741000002</v>
-      </c>
-      <c r="H52" s="20">
-        <v>0.030994505941249726</v>
-      </c>
-      <c r="I52" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J52" s="21" t="s">
+      <c r="B52" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J52" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
       <c r="B53" s="18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C53" s="19" t="s">
         <v>13</v>
@@ -2139,10 +2148,10 @@
         <v>13</v>
       </c>
       <c r="G53" s="19">
-        <v>10724.7482741</v>
+        <v>132.5360282999991</v>
       </c>
       <c r="H53" s="20">
-        <v>0.9999999999993497</v>
+        <v>0.012478822645782553</v>
       </c>
       <c r="I53" s="19" t="s">
         <v>13</v>
@@ -2151,21 +2160,38 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="2:9" ht="15" customHeight="1">
-      <c r="B56" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C56" s="22"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="22"/>
-      <c r="G56" s="22"/>
-      <c r="H56" s="22"/>
-      <c r="I56" s="22"/>
-    </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
+    <row r="54" spans="2:10" ht="15" customHeight="1">
+      <c r="B54" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C54" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54" s="19">
+        <v>10620.8760283</v>
+      </c>
+      <c r="H54" s="20">
+        <v>0.9999999999992826</v>
+      </c>
+      <c r="I54" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J54" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" ht="15" customHeight="1">
       <c r="B57" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C57" s="22"/>
       <c r="D57" s="22"/>
@@ -2173,10 +2199,11 @@
       <c r="F57" s="22"/>
       <c r="G57" s="22"/>
       <c r="H57" s="22"/>
+      <c r="I57" s="22"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C58" s="22"/>
       <c r="D58" s="22"/>
@@ -2185,9 +2212,9 @@
       <c r="G58" s="22"/>
       <c r="H58" s="22"/>
     </row>
-    <row r="59" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B59" s="23" t="s">
-        <v>65</v>
+    <row r="59" spans="2:8" ht="15" customHeight="1">
+      <c r="B59" s="13" t="s">
+        <v>67</v>
       </c>
       <c r="C59" s="22"/>
       <c r="D59" s="22"/>
@@ -2198,7 +2225,7 @@
     </row>
     <row r="60" spans="2:8" ht="27.6" customHeight="1">
       <c r="B60" s="23" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C60" s="22"/>
       <c r="D60" s="22"/>
@@ -2209,7 +2236,7 @@
     </row>
     <row r="61" spans="2:8" ht="27.6" customHeight="1">
       <c r="B61" s="23" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C61" s="22"/>
       <c r="D61" s="22"/>
@@ -2218,43 +2245,54 @@
       <c r="G61" s="22"/>
       <c r="H61" s="22"/>
     </row>
-    <row r="62" spans="2:7" ht="57.75" customHeight="1">
-      <c r="B62" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="C62" s="24"/>
-      <c r="D62" s="24"/>
-      <c r="E62" s="24"/>
-      <c r="F62" s="24"/>
-      <c r="G62" s="24"/>
-    </row>
-    <row r="65" ht="15">
-      <c r="B65" s="22" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="80" ht="15">
-      <c r="B80" s="22" t="s">
+    <row r="62" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B62" s="23" t="s">
         <v>70</v>
+      </c>
+      <c r="C62" s="22"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="22"/>
+      <c r="H62" s="22"/>
+    </row>
+    <row r="63" spans="2:7" ht="54" customHeight="1">
+      <c r="B63" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="C63" s="24"/>
+      <c r="D63" s="24"/>
+      <c r="E63" s="24"/>
+      <c r="F63" s="24"/>
+      <c r="G63" s="24"/>
+    </row>
+    <row r="66" ht="15">
+      <c r="B66" s="22" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="81" ht="15">
       <c r="B81" s="22" t="s">
-        <v>71</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="82" ht="15">
+      <c r="B82" s="22" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B57:I57"/>
     <mergeCell ref="B58:H58"/>
     <mergeCell ref="B59:H59"/>
     <mergeCell ref="B60:H60"/>
     <mergeCell ref="B61:H61"/>
-    <mergeCell ref="B62:G62"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B56:I56"/>
-    <mergeCell ref="B57:H57"/>
+    <mergeCell ref="B62:H62"/>
+    <mergeCell ref="B63:G63"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
